--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedAccount.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2585" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2449" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedAccount</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedAccount</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -449,45 +449,39 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Account.extension:anzahlVerlegungen</t>
-  </si>
-  <si>
-    <t>anzahlVerlegungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-anzahlVerlegungen}
+    <t>Account.extension:AnzahlVerlegungen</t>
+  </si>
+  <si>
+    <t>AnzahlVerlegungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-AnzahlVerlegungen}
 </t>
   </si>
   <si>
-    <t>AnzahlVerlegungen</t>
-  </si>
-  <si>
     <t>MOPED Extension für die Anzahl der Verlegungen</t>
   </si>
   <si>
-    <t>Account.extension:anzahlBeurlaubungen</t>
-  </si>
-  <si>
-    <t>anzahlBeurlaubungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-anzahlBeurlaubungen}
+    <t>Account.extension:AnzahlBeurlaubungen</t>
+  </si>
+  <si>
+    <t>AnzahlBeurlaubungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-AnzahlBeurlaubungen}
 </t>
   </si>
   <si>
-    <t>AnzahlBeurlaubungen</t>
-  </si>
-  <si>
     <t>MOPED Extension für die Anzahl der Beurlaubungen</t>
   </si>
   <si>
-    <t>Account.extension:workflowStatus</t>
-  </si>
-  <si>
-    <t>workflowStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-workflowStatus}
+    <t>Account.extension:WorkflowStatus</t>
+  </si>
+  <si>
+    <t>WorkflowStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-workflow-status}
 </t>
   </si>
   <si>
@@ -497,84 +491,20 @@
     <t>MOPED Extension für den Workflowstatus. Dieser beschreibt den Zustand in dem sich der administrative Fall derzeit befindet</t>
   </si>
   <si>
-    <t>Account.extension:verdachtArbeitsSchuelerunfall</t>
-  </si>
-  <si>
-    <t>verdachtArbeitsSchuelerunfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verdachtArbeitsSchuelerunfall}
+    <t>Account.extension:TageOhneKostenbeitrag</t>
+  </si>
+  <si>
+    <t>TageOhneKostenbeitrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-TageOhneKostenbeitrag}
 </t>
   </si>
   <si>
-    <t>Verdacht auf Arbeits- oder Schuelerunfall</t>
-  </si>
-  <si>
-    <t>MOPED Extension für den Verdacht auf einen Arbeits- oder Schuelerunfall.</t>
-  </si>
-  <si>
-    <t>Account.extension:verdachtFremdverschulden</t>
-  </si>
-  <si>
-    <t>verdachtFremdverschulden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verdachtFremdverschulden}
-</t>
-  </si>
-  <si>
-    <t>Verdacht auf Fremdverschulden</t>
-  </si>
-  <si>
-    <t>MOPED Extension für den Verdacht auf Fremdverschulden</t>
-  </si>
-  <si>
-    <t>Account.extension:tageOhneKostenbeitrag</t>
-  </si>
-  <si>
-    <t>tageOhneKostenbeitrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-tageOhneKostenbeitrag}
-</t>
-  </si>
-  <si>
     <t>Tage ohne Einhebung des Kostenbeitrags</t>
   </si>
   <si>
     <t>Anzahl der Tage, für welche kein Kostenbeitrag seitens der Krankenanstalt eingehoben wurde</t>
-  </si>
-  <si>
-    <t>Account.extension:coverageEligibilityRequestRef</t>
-  </si>
-  <si>
-    <t>coverageEligibilityRequestRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-coverageEligibilityRequestRef}
-</t>
-  </si>
-  <si>
-    <t>CoverageEligibilityRequest Referenz</t>
-  </si>
-  <si>
-    <t>Referenz vom Account auf den CoverageEligibilityRequest.</t>
-  </si>
-  <si>
-    <t>Account.extension:claimRef</t>
-  </si>
-  <si>
-    <t>claimRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-claimRef}
-</t>
-  </si>
-  <si>
-    <t>Claim Referenz</t>
-  </si>
-  <si>
-    <t>Referenz vom Account auf den Claim.</t>
   </si>
   <si>
     <t>Account.modifierExtension</t>
@@ -1603,12 +1533,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL76"/>
+  <dimension ref="A1:AL72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.40234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.92578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.22265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.32421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1616,7 +1546,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="86.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2650,10 +2580,10 @@
         <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2727,13 +2657,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -2755,13 +2685,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2835,13 +2765,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -2863,13 +2793,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2943,13 +2873,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -2971,13 +2901,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3051,44 +2981,46 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3136,7 +3068,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3154,7 +3086,7 @@
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15">
@@ -3162,11 +3094,9 @@
         <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3175,7 +3105,7 @@
         <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3184,16 +3114,16 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3244,7 +3174,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3256,31 +3186,29 @@
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C16" t="s" s="2">
         <v>170</v>
       </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>85</v>
@@ -3289,21 +3217,23 @@
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3328,13 +3258,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3352,37 +3282,35 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3400,16 +3328,16 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3436,13 +3364,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3460,19 +3388,19 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3483,46 +3411,42 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3546,13 +3470,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3576,38 +3500,38 @@
         <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>130</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3619,13 +3543,13 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3676,13 +3600,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3691,50 +3615,50 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3760,13 +3684,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3784,13 +3708,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -3799,18 +3723,18 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3833,15 +3757,17 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3866,13 +3792,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3890,7 +3816,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3905,18 +3831,18 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>20</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3927,7 +3853,7 @@
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3939,15 +3865,17 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3972,13 +3900,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -3996,13 +3924,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4011,22 +3939,22 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4042,16 +3970,16 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4102,7 +4030,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4111,28 +4039,28 @@
         <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>222</v>
+        <v>158</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4148,19 +4076,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>226</v>
+        <v>161</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4210,7 +4138,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4222,55 +4150,57 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4318,33 +4248,33 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>235</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4352,10 +4282,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4367,17 +4297,15 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4426,13 +4354,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4444,19 +4372,19 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4472,10 +4400,10 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>243</v>
@@ -4483,7 +4411,9 @@
       <c r="M27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N27" s="2"/>
+      <c r="N27" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4532,7 +4462,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4541,35 +4471,35 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4578,10 +4508,10 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>249</v>
@@ -4589,9 +4519,7 @@
       <c r="M28" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>183</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4640,25 +4568,25 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="29">
@@ -4670,26 +4598,26 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>132</v>
+        <v>253</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>254</v>
@@ -4697,12 +4625,8 @@
       <c r="M29" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>184</v>
-      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4750,25 +4674,25 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>130</v>
       </c>
     </row>
     <row r="30">
@@ -4784,10 +4708,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4796,16 +4720,16 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4859,10 +4783,10 @@
         <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -4874,19 +4798,19 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4902,20 +4826,18 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>194</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4964,7 +4886,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4973,35 +4895,35 @@
         <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>268</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5010,18 +4932,20 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5070,65 +4994,69 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>273</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>275</v>
+        <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5176,33 +5104,33 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>278</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5210,10 +5138,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5225,13 +5153,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5282,13 +5210,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5300,15 +5228,15 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5331,13 +5259,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5388,7 +5316,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5397,35 +5325,35 @@
         <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>247</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5437,17 +5365,15 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5496,37 +5422,37 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>247</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5539,26 +5465,22 @@
         <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5606,7 +5528,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5618,21 +5540,21 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>138</v>
+        <v>281</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5640,7 +5562,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>85</v>
@@ -5655,13 +5577,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>287</v>
+        <v>194</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>288</v>
+        <v>221</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>289</v>
+        <v>222</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5712,44 +5634,44 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>290</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -5761,15 +5683,17 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>292</v>
+        <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5818,65 +5742,69 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>291</v>
+        <v>229</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>295</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -5924,33 +5852,33 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>299</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5961,7 +5889,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5970,16 +5898,16 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6030,19 +5958,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>303</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6053,18 +5981,18 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>85</v>
@@ -6076,16 +6004,16 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>216</v>
+        <v>290</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6112,13 +6040,11 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6136,44 +6062,44 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6185,17 +6111,15 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>132</v>
+        <v>296</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6244,37 +6168,37 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6287,26 +6211,22 @@
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6330,13 +6250,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6354,7 +6274,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6366,21 +6286,21 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6403,13 +6323,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6460,7 +6380,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6483,21 +6403,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6506,16 +6426,16 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>312</v>
+        <v>179</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6542,11 +6462,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6564,16 +6486,16 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>97</v>
@@ -6587,10 +6509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6601,7 +6523,7 @@
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6610,16 +6532,16 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6670,19 +6592,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -6693,10 +6615,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6707,7 +6629,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -6719,13 +6641,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>321</v>
+        <v>221</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>322</v>
+        <v>222</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6752,13 +6674,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -6776,44 +6698,44 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>320</v>
+        <v>223</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -6825,15 +6747,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>292</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -6882,37 +6806,37 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6925,22 +6849,26 @@
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -6964,10 +6892,10 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>20</v>
@@ -6988,7 +6916,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>234</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7000,21 +6928,21 @@
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7025,7 +6953,7 @@
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7034,16 +6962,16 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7094,19 +7022,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>336</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7117,18 +7045,18 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>85</v>
@@ -7140,16 +7068,16 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>243</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>244</v>
+        <v>324</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7176,13 +7104,11 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>20</v>
+        <v>325</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7200,44 +7126,44 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>245</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7249,17 +7175,15 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>296</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7308,37 +7232,37 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>251</v>
+        <v>327</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7351,26 +7275,22 @@
         <v>20</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>254</v>
+        <v>331</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -7394,10 +7314,10 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>20</v>
@@ -7418,7 +7338,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7430,21 +7350,21 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7455,7 +7375,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7467,13 +7387,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>264</v>
+        <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7500,10 +7420,10 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>20</v>
@@ -7524,13 +7444,13 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -7547,21 +7467,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -7573,13 +7493,13 @@
         <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7606,11 +7526,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -7628,16 +7550,16 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>97</v>
@@ -7651,10 +7573,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7665,7 +7587,7 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -7677,13 +7599,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7734,16 +7656,16 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>97</v>
@@ -7757,10 +7679,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7771,7 +7693,7 @@
         <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -7783,13 +7705,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>353</v>
+        <v>221</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>354</v>
+        <v>222</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7816,10 +7738,10 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>20</v>
@@ -7840,37 +7762,37 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>352</v>
+        <v>223</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7889,15 +7811,17 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>330</v>
+        <v>227</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -7922,10 +7846,10 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>20</v>
@@ -7946,7 +7870,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>356</v>
+        <v>229</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -7958,25 +7882,25 @@
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -7989,22 +7913,26 @@
         <v>20</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>359</v>
+        <v>132</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>360</v>
+        <v>232</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8052,7 +7980,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>358</v>
+        <v>234</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8064,21 +7992,21 @@
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8089,7 +8017,7 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8101,13 +8029,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8134,13 +8062,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8158,13 +8086,13 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
@@ -8181,10 +8109,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8192,7 +8120,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>85</v>
@@ -8207,13 +8135,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>216</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>243</v>
+        <v>353</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>244</v>
+        <v>354</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8264,44 +8192,44 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>245</v>
+        <v>351</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -8313,17 +8241,15 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>249</v>
+        <v>356</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -8348,13 +8274,11 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -8372,37 +8296,37 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>251</v>
+        <v>355</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8415,26 +8339,22 @@
         <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>254</v>
+        <v>360</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -8482,7 +8402,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>256</v>
+        <v>359</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8494,21 +8414,21 @@
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8531,13 +8451,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>369</v>
+        <v>221</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>370</v>
+        <v>222</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8564,13 +8484,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -8588,7 +8508,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>368</v>
+        <v>223</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8597,35 +8517,35 @@
         <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -8637,15 +8557,17 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>374</v>
+        <v>132</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>375</v>
+        <v>227</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -8694,65 +8616,69 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>373</v>
+        <v>229</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>378</v>
+        <v>232</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
       </c>
@@ -8776,11 +8702,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -8798,33 +8726,33 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>377</v>
+        <v>234</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8835,7 +8763,7 @@
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -8847,13 +8775,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8880,13 +8808,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>20</v>
+        <v>368</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>20</v>
+        <v>370</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -8904,13 +8832,13 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
@@ -8927,10 +8855,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8953,13 +8881,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>243</v>
+        <v>372</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>244</v>
+        <v>373</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8986,13 +8914,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>20</v>
+        <v>368</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9010,7 +8938,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>245</v>
+        <v>371</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9019,35 +8947,35 @@
         <v>85</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9059,17 +8987,15 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>132</v>
+        <v>270</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>249</v>
+        <v>376</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9118,69 +9044,65 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>251</v>
+        <v>375</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>132</v>
+        <v>379</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>254</v>
+        <v>380</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>20</v>
       </c>
@@ -9228,33 +9150,33 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>256</v>
+        <v>378</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9277,15 +9199,17 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>201</v>
+        <v>383</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -9310,13 +9234,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -9334,7 +9258,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9352,432 +9276,6 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL76" t="s" s="2">
         <v>20</v>
       </c>
     </row>
